--- a/StructureDefinition-Prov-id.xlsx
+++ b/StructureDefinition-Prov-id.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:41:45+00:00</t>
+    <t>2026-09-18T09:59:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Prov-id.xlsx
+++ b/StructureDefinition-Prov-id.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T09:59:15+00:00</t>
+    <t>2026-09-18T10:29:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
